--- a/data/trans_bre/P16A08-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A08-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,74</t>
+          <t>-0,99; 1,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,32</t>
+          <t>0,35; 4,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 2,97</t>
+          <t>-0,94; 2,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 3,3</t>
+          <t>-1,27; 3,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-46,17; 157,19</t>
+          <t>-45,37; 171,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,69; 305,71</t>
+          <t>0,31; 303,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-33,41; 170,0</t>
+          <t>-27,68; 148,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-29,2; 155,25</t>
+          <t>-28,82; 158,98</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,99</t>
+          <t>-0,48; 2,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 4,04</t>
+          <t>0,38; 4,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,89</t>
+          <t>1,17; 4,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,96</t>
+          <t>-1,03; 3,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 179,98</t>
+          <t>-14,58; 173,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 154,41</t>
+          <t>8,06; 150,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,66; 236,07</t>
+          <t>29,53; 224,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-25,81; 194,8</t>
+          <t>-27,41; 196,73</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 4,08</t>
+          <t>0,39; 4,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,98</t>
+          <t>-0,72; 3,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,15</t>
+          <t>1,62; 6,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 1,84</t>
+          <t>-3,61; 1,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,12; 287,47</t>
+          <t>3,45; 307,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 131,64</t>
+          <t>-16,32; 129,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,69; 275,82</t>
+          <t>34,02; 277,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-56,99; 52,05</t>
+          <t>-60,07; 44,15</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,75</t>
+          <t>0,19; 3,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 4,15</t>
+          <t>0,23; 4,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 3,12</t>
+          <t>-0,39; 3,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 25,34</t>
+          <t>2,14; 27,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,48; 167,61</t>
+          <t>2,02; 170,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,29; 147,28</t>
+          <t>3,67; 152,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 117,31</t>
+          <t>-9,3; 115,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>60,22; 1087,09</t>
+          <t>63,93; 1382,18</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,4</t>
+          <t>0,64; 2,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,07</t>
+          <t>1,09; 3,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,35</t>
+          <t>1,4; 3,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 9,9</t>
+          <t>0,8; 10,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,03; 121,72</t>
+          <t>22,13; 120,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,38; 101,25</t>
+          <t>28,35; 108,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,06; 126,06</t>
+          <t>39,55; 124,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,15; 336,51</t>
+          <t>22,8; 330,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A08-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A08-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,02</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,88</t>
+          <t>-1,01; 1,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,29</t>
+          <t>0,41; 4,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 2,73</t>
+          <t>-1,05; 2,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,21</t>
+          <t>-0,96; 3,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,37; 171,98</t>
+          <t>-45,29; 174,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 303,75</t>
+          <t>8,9; 322,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-27,68; 148,69</t>
+          <t>-32,71; 151,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-28,82; 158,98</t>
+          <t>-23,23; 152,56</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,75</t>
+          <t>-0,43; 3,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,21</t>
+          <t>0,25; 4,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,78</t>
+          <t>1,32; 4,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 3,19</t>
+          <t>-0,98; 2,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 173,71</t>
+          <t>-18,24; 171,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,06; 150,57</t>
+          <t>3,26; 143,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,53; 224,73</t>
+          <t>31,55; 229,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,41; 196,73</t>
+          <t>-26,03; 97,17</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>1,77</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-9,73%</t>
+          <t>41,46%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,05</t>
+          <t>0,37; 4,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 3,95</t>
+          <t>-0,75; 4,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 6,17</t>
+          <t>1,68; 6,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 1,7</t>
+          <t>-0,36; 3,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 307,37</t>
+          <t>7,96; 304,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 129,41</t>
+          <t>-16,28; 137,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,02; 277,28</t>
+          <t>37,33; 263,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-60,07; 44,15</t>
+          <t>-8,73; 125,17</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,7</t>
+          <t>2,69</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>292,31%</t>
+          <t>87,72%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,83</t>
+          <t>0,04; 3,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 4,25</t>
+          <t>0,25; 4,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 3,2</t>
+          <t>-0,59; 3,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 27,5</t>
+          <t>0,93; 4,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 170,26</t>
+          <t>0,63; 173,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,67; 152,25</t>
+          <t>5,0; 161,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 115,07</t>
+          <t>-13,63; 119,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>63,93; 1382,18</t>
+          <t>20,88; 207,03</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,02</t>
+          <t>1,57</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>46,36%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,37</t>
+          <t>0,74; 2,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,15</t>
+          <t>1,09; 3,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,27</t>
+          <t>1,37; 3,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 10,65</t>
+          <t>0,59; 2,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,13; 120,77</t>
+          <t>25,93; 123,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,35; 108,2</t>
+          <t>27,76; 103,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,55; 124,15</t>
+          <t>38,82; 122,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,8; 330,72</t>
+          <t>14,09; 85,7</t>
         </is>
       </c>
     </row>
